--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-specimen.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-specimen.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="200">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -586,6 +586,10 @@
   </si>
   <si>
     <t>fr-lm-specimen.collection.bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-body-structure
+</t>
   </si>
   <si>
     <t>Localisation du prélèvement</t>
@@ -4311,13 +4315,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4385,10 +4389,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4414,10 +4418,10 @@
         <v>127</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4468,7 +4472,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -4485,10 +4489,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4514,10 +4518,10 @@
         <v>80</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4568,7 +4572,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -4585,10 +4589,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4614,10 +4618,10 @@
         <v>172</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4668,7 +4672,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -4685,10 +4689,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4714,10 +4718,10 @@
         <v>103</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4768,7 +4772,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -4785,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4814,10 +4818,10 @@
         <v>131</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4847,7 +4851,7 @@
         <v>73</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z39" t="s" s="2">
         <v>73</v>
@@ -4868,7 +4872,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -4885,10 +4889,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4911,13 +4915,13 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -4968,7 +4972,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-specimen.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,11 +269,11 @@
     <t>fr-lm-specimen.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 </t>
   </si>
   <si>
-    <t>Patient/subject information</t>
+    <t>Patient / Usager</t>
   </si>
   <si>
     <t>fr-lm-entry.header.subject</t>
@@ -443,7 +443,7 @@
     <t>fr-lm-entry.header.source</t>
   </si>
   <si>
-    <t>fr-lm-specimen.header.langue</t>
+    <t>fr-lm-specimen.header.language</t>
   </si>
   <si>
     <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
@@ -451,7 +451,7 @@
 La partie en majuscules indique le code pays (ISO-3166)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.langue</t>
+    <t>fr-lm-entry.header.language</t>
   </si>
   <si>
     <t>fr-lm-specimen.identifier</t>
@@ -484,7 +484,7 @@
     <t>fr-lm-specimen.specimenSource[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-locationhttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device</t>
   </si>
   <si>
@@ -530,7 +530,7 @@
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
-https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisationhttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usagerhttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-related-person</t>
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisationhttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patienthttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-related-person</t>
   </si>
   <si>
     <t>Organisation prélevante</t>
@@ -950,7 +950,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="207.421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="201.46484375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-specimen.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-specimen.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="197">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -422,13 +422,13 @@
 </t>
   </si>
   <si>
-    <t>Statut de l'acte</t>
-  </si>
-  <si>
-    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+    <t>Disponibilité du prélèvement</t>
+  </si>
+  <si>
+    <t>Statut</t>
+  </si>
+  <si>
+    <t>(preferred): HL7 specimen-status</t>
   </si>
   <si>
     <t>fr-lm-entry.header.status</t>
@@ -458,15 +458,6 @@
   </si>
   <si>
     <t>Identifiant unique de l'échantillon, au sein d'un périmètre défini. Exemple : identifiant attribué par le système du préleveur, identifiant attribué par le laboratoire, etc. Plusieurs identifiants peuvent être utilisés.</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.status</t>
-  </si>
-  <si>
-    <t>Disponibilité du prélèvement</t>
-  </si>
-  <si>
-    <t>(preferred): HL7 specimen-status</t>
   </si>
   <si>
     <t>fr-lm-specimen.type</t>
@@ -937,7 +928,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ40"/>
+  <dimension ref="A1:AJ39"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.10546875" customWidth="true" bestFit="true"/>
@@ -965,7 +956,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="49.875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.1796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -2600,7 +2591,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
@@ -2621,7 +2612,7 @@
         <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2651,10 +2642,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2675,7 +2666,7 @@
         <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -3054,7 +3045,7 @@
         <v>146</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>73</v>
@@ -3089,10 +3080,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3115,13 +3106,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3151,10 +3142,10 @@
         <v>73</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>73</v>
@@ -3172,7 +3163,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3203,7 +3194,7 @@
         <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>73</v>
@@ -3278,7 +3269,7 @@
         <v>74</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>73</v>
@@ -3403,7 +3394,7 @@
         <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>73</v>
@@ -3415,13 +3406,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L25" t="s" s="2">
-        <v>159</v>
-      </c>
       <c r="M25" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3451,7 +3442,7 @@
         <v>73</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>73</v>
@@ -3478,7 +3469,7 @@
         <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>73</v>
@@ -3503,7 +3494,7 @@
         <v>74</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>73</v>
@@ -3515,7 +3506,7 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>161</v>
@@ -3551,7 +3542,7 @@
         <v>73</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>162</v>
+        <v>73</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>73</v>
@@ -3578,7 +3569,7 @@
         <v>74</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>73</v>
@@ -3589,10 +3580,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3603,7 +3594,7 @@
         <v>74</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>73</v>
@@ -3615,7 +3606,7 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>164</v>
@@ -3672,13 +3663,13 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>73</v>
@@ -3700,7 +3691,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>79</v>
@@ -3775,7 +3766,7 @@
         <v>165</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>79</v>
@@ -3800,7 +3791,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>79</v>
@@ -3875,7 +3866,7 @@
         <v>168</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>79</v>
@@ -3915,13 +3906,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="M30" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3951,7 +3942,7 @@
         <v>73</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>73</v>
+        <v>173</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>73</v>
@@ -4003,7 +3994,7 @@
         <v>74</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>73</v>
@@ -4015,13 +4006,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4051,7 +4042,7 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>176</v>
+        <v>73</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>73</v>
@@ -4078,7 +4069,7 @@
         <v>74</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>73</v>
@@ -4203,7 +4194,7 @@
         <v>74</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>73</v>
@@ -4278,7 +4269,7 @@
         <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>73</v>
@@ -4300,7 +4291,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>79</v>
@@ -4315,13 +4306,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="L34" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="M34" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4375,7 +4366,7 @@
         <v>183</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>79</v>
@@ -4389,10 +4380,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4400,10 +4391,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>73</v>
@@ -4415,13 +4406,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>127</v>
+        <v>80</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4472,13 +4463,13 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>73</v>
@@ -4489,10 +4480,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4503,7 +4494,7 @@
         <v>74</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>73</v>
@@ -4515,13 +4506,13 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>80</v>
+        <v>169</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4572,13 +4563,13 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>73</v>
@@ -4589,10 +4580,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4600,7 +4591,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>79</v>
@@ -4615,13 +4606,13 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>172</v>
+        <v>103</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4672,10 +4663,10 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>79</v>
@@ -4689,10 +4680,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4700,10 +4691,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>73</v>
@@ -4715,13 +4706,13 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4751,7 +4742,7 @@
         <v>73</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>73</v>
+        <v>193</v>
       </c>
       <c r="Z38" t="s" s="2">
         <v>73</v>
@@ -4772,13 +4763,13 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>73</v>
@@ -4803,7 +4794,7 @@
         <v>74</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>73</v>
@@ -4815,13 +4806,13 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>131</v>
+        <v>195</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4851,7 +4842,7 @@
         <v>73</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>196</v>
+        <v>73</v>
       </c>
       <c r="Z39" t="s" s="2">
         <v>73</v>
@@ -4878,112 +4869,12 @@
         <v>74</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K40" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
-      <c r="P40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q40" s="2"/>
-      <c r="R40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-specimen.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
